--- a/Data/Excel/Drop.xlsx
+++ b/Data/Excel/Drop.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\ProjectBB\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C6B77B7-210E-42D4-A344-991C981B522C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3FE6A13-583B-46F6-B00C-4F44058A14EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7452" yWindow="4188" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시트1" sheetId="1" r:id="rId1"/>
@@ -25,59 +25,80 @@
     <t>ID</t>
   </si>
   <si>
-    <t>string</t>
-  </si>
-  <si>
     <t>int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>float</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>drop1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>drop2</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>drop3</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>drop4</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>drop5</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>min</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>max</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>rate</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>itemid</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>id:Item</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>신선한 우유</t>
+  </si>
+  <si>
+    <t>버터</t>
+  </si>
+  <si>
+    <t>멧돼지 고기</t>
+  </si>
+  <si>
+    <t>양 고기</t>
   </si>
   <si>
     <r>
-      <t>i</t>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>정체불명의</t>
     </r>
     <r>
       <rPr>
@@ -87,132 +108,31 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>tem1</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>i</t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>tem2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
+        <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t/>
+      <t>말린고기</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <t>i</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>tem3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>i</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>tem4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>i</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>tem5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t/>
-    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -248,6 +168,21 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -259,7 +194,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -336,29 +271,76 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -584,6 +566,7 @@
     <col min="2" max="2" width="16.77734375" customWidth="1"/>
     <col min="3" max="3" width="34.109375" customWidth="1"/>
     <col min="4" max="4" width="65.21875" customWidth="1"/>
+    <col min="5" max="5" width="22.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18" thickBot="1">
@@ -591,122 +574,122 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="13.8" thickBot="1">
       <c r="A2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>2</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18" thickBot="1">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:5" ht="16.2" thickBot="1">
+      <c r="A3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="7">
+        <v>10</v>
+      </c>
+      <c r="C3" s="8">
+        <v>15</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16.2" thickBot="1">
+      <c r="A4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2">
-        <v>10</v>
-      </c>
-      <c r="C3" s="4">
-        <v>15</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="18" thickBot="1">
-      <c r="A4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="6">
+      <c r="B4" s="9">
         <v>20</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="10">
         <v>25</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="10">
         <v>0.2</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="12" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="6">
+      <c r="A5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="9">
         <v>30</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="10">
         <v>35</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="10">
         <v>0.3</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="12" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="6">
+      <c r="A6" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="9">
         <v>40</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="10">
         <v>45</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="10">
         <v>0.3</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="12" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="6">
+      <c r="A7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="9">
         <v>50</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="10">
         <v>55</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="10">
         <v>0.1</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="13" t="s">
         <v>18</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data/Excel/Drop.xlsx
+++ b/Data/Excel/Drop.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\ProjectBB\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3FE6A13-583B-46F6-B00C-4F44058A14EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4FB4BF7-47BE-4678-B1A1-97B28FA71F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7452" yWindow="4188" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5112" yWindow="4428" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시트1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>ID</t>
   </si>
@@ -122,6 +122,13 @@
       <t>말린고기</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop6</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>순록 고기</t>
   </si>
 </sst>
 </file>
@@ -194,7 +201,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -301,11 +308,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -341,6 +370,12 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -560,7 +595,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="16.77734375" customWidth="1"/>
@@ -688,6 +723,23 @@
         <v>18</v>
       </c>
     </row>
+    <row r="8" spans="1:5" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="14">
+        <v>30</v>
+      </c>
+      <c r="C8" s="15">
+        <v>20</v>
+      </c>
+      <c r="D8" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
